--- a/make_interface/Maule Robust Regression.xlsx
+++ b/make_interface/Maule Robust Regression.xlsx
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9.23°</t>
+          <t>-3.27°</t>
         </is>
       </c>
     </row>
@@ -456,7 +456,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.35°</t>
+          <t>-8.77°</t>
         </is>
       </c>
     </row>
@@ -466,7 +466,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-6.60°</t>
+          <t>-14.04°</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-14.20°</t>
+          <t>-18.97°</t>
         </is>
       </c>
     </row>
@@ -486,7 +486,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.11°</t>
+          <t>-23.51°</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-27.18°</t>
+          <t>-27.62°</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-32.41°</t>
+          <t>-31.31°</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-36.86°</t>
+          <t>-34.62°</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-40.16°</t>
+          <t>-37.19°</t>
         </is>
       </c>
     </row>
